--- a/Real Estate Portfolio Analysis - Pham (2026).xlsx
+++ b/Real Estate Portfolio Analysis - Pham (2026).xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30215"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4042CD6B-BAC9-434D-AD28-EE6DFF9DE4C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DDF4796D-E1F1-443C-B6C4-177899EE41EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="40" r:id="rId7"/>
+    <pivotCache cacheId="387" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="137">
   <si>
     <t>Portfolio Dashboard</t>
   </si>
@@ -261,13 +261,16 @@
     <t>Cash</t>
   </si>
   <si>
+    <t>AC Filter Replaced</t>
+  </si>
+  <si>
     <t>Thomas</t>
   </si>
   <si>
     <t>Aaron</t>
   </si>
   <si>
-    <t>Replaced broken window (RESOLVED), paid for pet fee</t>
+    <t>Replaced broken window (RESOLVED), paid for pet fee, AC Filter Replaced</t>
   </si>
   <si>
     <t>Michael</t>
@@ -276,7 +279,7 @@
     <t>Dorothy</t>
   </si>
   <si>
-    <t>Wanted to renew lease early</t>
+    <t>Wanted to renew lease early, AC Filter Replaced</t>
   </si>
   <si>
     <t>David</t>
@@ -306,13 +309,16 @@
     <t>New electric water heater shut down, replaced fuses (RESOLVED)</t>
   </si>
   <si>
-    <t>Husband not home/Did not respond to texts</t>
-  </si>
-  <si>
     <t>Requested lease renewal but only in her name, not husband (She feels like husband does not help with bills)</t>
   </si>
   <si>
     <t>Fixing to move out due to extra baby, paid this month, Security deposit returned (-$800)</t>
+  </si>
+  <si>
+    <t>Roof leak, currently getting quotes for roof replacement due to age</t>
+  </si>
+  <si>
+    <t>Tenant's son car crash, son is okay but car totalled</t>
   </si>
   <si>
     <t>Category</t>
@@ -2328,6 +2334,9 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="12" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+    </dxf>
+    <dxf>
       <border outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -2342,9 +2351,6 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="12" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     </dxf>
     <dxf>
       <border outline="0">
@@ -3750,37 +3756,37 @@
                 <c:formatCode>"$"#,##0</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>724.80399999999997</c:v>
+                  <c:v>884.80399999999997</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>900</c:v>
+                  <c:v>1080</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>475</c:v>
+                  <c:v>570</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>731.08199999999999</c:v>
+                  <c:v>881.08199999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>727.23</c:v>
+                  <c:v>1067.23</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>852.05200000000002</c:v>
+                  <c:v>1032.0519999999999</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>796.08600000000001</c:v>
+                  <c:v>956.08600000000001</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>525</c:v>
+                  <c:v>630</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>674.14200000000005</c:v>
+                  <c:v>844.14200000000005</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>525</c:v>
+                  <c:v>630</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>850</c:v>
+                  <c:v>1020</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0</c:v>
@@ -6006,94 +6012,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E389D1D9-8454-4090-A4FC-E5E15064BF2B}" name="CategoryAnalysis" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="9">
-    <pivotField compact="0" numFmtId="14" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
-      <items count="5">
-        <item x="3"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" numFmtId="166" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Amount" fld="4" baseField="0" baseItem="0" numFmtId="8"/>
-  </dataFields>
-  <formats count="7">
-    <format dxfId="86">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="87">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="88">
-      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="89">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="2" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="90">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="91">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="92">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleMedium9" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{72787D74-588F-472E-A9F9-2443F0635269}" name="TotalPivotTable" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{72787D74-588F-472E-A9F9-2443F0635269}" name="TotalPivotTable" cacheId="387" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A12:H21" firstHeaderRow="1" firstDataRow="2" firstDataCol="2"/>
   <pivotFields count="9">
     <pivotField compact="0" numFmtId="14" outline="0" showAll="0"/>
@@ -6191,19 +6110,113 @@
     <dataField name="Sum of Amount" fld="4" baseField="0" baseItem="0" numFmtId="8"/>
   </dataFields>
   <formats count="8">
-    <format dxfId="78">
+    <format dxfId="85">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="79">
+    <format dxfId="86">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
+    <format dxfId="87">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
+    </format>
+    <format dxfId="88">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="89">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="90">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="7" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="91">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="92">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleMedium9" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E389D1D9-8454-4090-A4FC-E5E15064BF2B}" name="CategoryAnalysis" cacheId="387" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField compact="0" numFmtId="14" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="5">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" numFmtId="166" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Amount" fld="4" baseField="0" baseItem="0" numFmtId="8"/>
+  </dataFields>
+  <formats count="7">
+    <format dxfId="78">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="79">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
     <format dxfId="80">
-      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
     <format dxfId="81">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="1" count="0"/>
+          <reference field="2" count="0"/>
         </references>
       </pivotArea>
     </format>
@@ -6211,16 +6224,9 @@
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
     <format dxfId="83">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="7" count="0"/>
-        </references>
-      </pivotArea>
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
     <format dxfId="84">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="85">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -6755,7 +6761,7 @@
       </c>
       <c r="AB4" s="4">
         <f>IF(Actuals!I2="No data",0,Actuals!I2)</f>
-        <v>724.80399999999997</v>
+        <v>884.80399999999997</v>
       </c>
     </row>
     <row r="5" spans="1:28">
@@ -6788,7 +6794,7 @@
       </c>
       <c r="AB5" s="4">
         <f>IF(Actuals!I3="No data",0,Actuals!I3)</f>
-        <v>900</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="6" spans="1:28">
@@ -6821,7 +6827,7 @@
       </c>
       <c r="AB6" s="4">
         <f>IF(Actuals!I4="No data",0,Actuals!I4)</f>
-        <v>475</v>
+        <v>570</v>
       </c>
     </row>
     <row r="7" spans="1:28">
@@ -6854,7 +6860,7 @@
       </c>
       <c r="AB7" s="4">
         <f>IF(Actuals!I5="No data",0,Actuals!I5)</f>
-        <v>731.08199999999999</v>
+        <v>881.08199999999999</v>
       </c>
     </row>
     <row r="8" spans="1:28">
@@ -6887,7 +6893,7 @@
       </c>
       <c r="AB8" s="4">
         <f>IF(Actuals!I6="No data",0,Actuals!I6)</f>
-        <v>727.23</v>
+        <v>1067.23</v>
       </c>
     </row>
     <row r="9" spans="1:28">
@@ -6920,7 +6926,7 @@
       </c>
       <c r="AB9" s="4">
         <f>IF(Actuals!I7="No data",0,Actuals!I7)</f>
-        <v>852.05200000000002</v>
+        <v>1032.0519999999999</v>
       </c>
     </row>
     <row r="10" spans="1:28">
@@ -6946,7 +6952,7 @@
       </c>
       <c r="AB10" s="4">
         <f>IF(Actuals!I8="No data",0,Actuals!I8)</f>
-        <v>796.08600000000001</v>
+        <v>956.08600000000001</v>
       </c>
     </row>
     <row r="11" spans="1:28" ht="18.75">
@@ -6975,7 +6981,7 @@
       </c>
       <c r="AB11" s="4">
         <f>IF(Actuals!I9="No data",0,Actuals!I9)</f>
-        <v>525</v>
+        <v>630</v>
       </c>
     </row>
     <row r="12" spans="1:28">
@@ -7002,7 +7008,7 @@
       </c>
       <c r="AB12" s="4">
         <f>IF(Actuals!I10="No data",0,Actuals!I10)</f>
-        <v>674.14200000000005</v>
+        <v>844.14200000000005</v>
       </c>
     </row>
     <row r="13" spans="1:28">
@@ -7011,7 +7017,7 @@
       </c>
       <c r="B13" s="35">
         <f>IFERROR(SUMIF(Actuals!D2:D1000,"&lt;&gt;No data",Actuals!D2:D1000),0)</f>
-        <v>-100</v>
+        <v>1715</v>
       </c>
       <c r="V13" t="str">
         <f>Inputs!A12</f>
@@ -7035,7 +7041,7 @@
       </c>
       <c r="AB13" s="4">
         <f>IF(Actuals!I11="No data",0,Actuals!I11)</f>
-        <v>525</v>
+        <v>630</v>
       </c>
     </row>
     <row r="14" spans="1:28">
@@ -7068,7 +7074,7 @@
       </c>
       <c r="AB14" s="4">
         <f>IF(Actuals!I12="No data",0,Actuals!I12)</f>
-        <v>850</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="15" spans="1:28">
@@ -7077,7 +7083,7 @@
       </c>
       <c r="B15" s="35">
         <f>IFERROR(SUMIF(Actuals!J2:J1000,"&lt;&gt;No data",Actuals!J2:J1000),0)</f>
-        <v>556.22933333333344</v>
+        <v>2371.2293333333332</v>
       </c>
       <c r="V15" t="str">
         <f>Inputs!A14</f>
@@ -7110,7 +7116,7 @@
       </c>
       <c r="B16" s="22">
         <f>IFERROR(COUNTIF(Actuals!J2:J1000,"&lt;0"),0)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C16" s="67" t="s">
         <v>18</v>
@@ -7255,11 +7261,11 @@
       </c>
       <c r="C2" s="61">
         <f>IFERROR(IF(SUMIF('Rent Collections'!$B$2:$B$10007,A2,'Rent Collections'!$E$2:$E$10007)=0,"No data",SUMIF('Rent Collections'!$B$2:$B$10007,A2,'Rent Collections'!$E$2:$E$10007)/(COUNTIFS('Rent Collections'!$B$2:$B$10000,"1053 Ridgeway Avenue")-1)),"No data")</f>
-        <v>800</v>
+        <v>960</v>
       </c>
       <c r="D2" s="36">
         <f t="shared" ref="D2:D14" si="0">IFERROR(IF(C2="No data","No data",C2-B2),"No data")</f>
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="E2" s="35">
         <f>IFERROR(Inputs!H3,"N/A")</f>
@@ -7279,11 +7285,11 @@
       </c>
       <c r="I2" s="36">
         <f t="shared" ref="I2:I14" si="2">IFERROR(IF(OR(C2="No data",F2="No data"),"No data",C2-F2),"No data")</f>
-        <v>724.80399999999997</v>
+        <v>884.80399999999997</v>
       </c>
       <c r="J2" s="42">
         <f t="shared" ref="J2:J14" si="3">IFERROR(IF(I2="No data","No data",I2-H2),"No data")</f>
-        <v>31.470666666666602</v>
+        <v>191.4706666666666</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -7297,11 +7303,11 @@
       </c>
       <c r="C3" s="61">
         <f>IFERROR(IF(SUMIF('Rent Collections'!$B$2:$B$10007,A3,'Rent Collections'!$E$2:$E$10007)=0,"No data",SUMIF('Rent Collections'!$B$2:$B$10007,A3,'Rent Collections'!$E$2:$E$10007)/(COUNTIFS('Rent Collections'!$B$2:$B$10000,"1053 Ridgeway Avenue")-1)),"No data")</f>
-        <v>900</v>
+        <v>1080</v>
       </c>
       <c r="D3" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="E3" s="35">
         <f>IFERROR(Inputs!H4,"N/A")</f>
@@ -7321,11 +7327,11 @@
       </c>
       <c r="I3" s="36">
         <f t="shared" si="2"/>
-        <v>900</v>
+        <v>1080</v>
       </c>
       <c r="J3" s="42">
         <f t="shared" si="3"/>
-        <v>120</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -7339,11 +7345,11 @@
       </c>
       <c r="C4" s="61">
         <f>IFERROR(IF(SUMIF('Rent Collections'!$B$2:$B$10007,A4,'Rent Collections'!$E$2:$E$10007)=0,"No data",SUMIF('Rent Collections'!$B$2:$B$10007,A4,'Rent Collections'!$E$2:$E$10007)/(COUNTIFS('Rent Collections'!$B$2:$B$10000,"1053 Ridgeway Avenue")-1)),"No data")</f>
-        <v>475</v>
+        <v>570</v>
       </c>
       <c r="D4" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="E4" s="35">
         <f>IFERROR(Inputs!H5,"N/A")</f>
@@ -7363,11 +7369,11 @@
       </c>
       <c r="I4" s="36">
         <f t="shared" si="2"/>
-        <v>475</v>
+        <v>570</v>
       </c>
       <c r="J4" s="42">
         <f t="shared" si="3"/>
-        <v>49.083333333333314</v>
+        <v>144.08333333333331</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -7381,11 +7387,11 @@
       </c>
       <c r="C5" s="61">
         <f>IFERROR(IF(SUMIF('Rent Collections'!$B$2:$B$10007,A5,'Rent Collections'!$E$2:$E$10007)=0,"No data",SUMIF('Rent Collections'!$B$2:$B$10007,A5,'Rent Collections'!$E$2:$E$10007)/(COUNTIFS('Rent Collections'!$B$2:$B$10000,"1053 Ridgeway Avenue")-1)),"No data")</f>
-        <v>750</v>
+        <v>900</v>
       </c>
       <c r="D5" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="E5" s="35">
         <f>IFERROR(Inputs!H6,"N/A")</f>
@@ -7405,11 +7411,11 @@
       </c>
       <c r="I5" s="36">
         <f t="shared" si="2"/>
-        <v>731.08199999999999</v>
+        <v>881.08199999999999</v>
       </c>
       <c r="J5" s="42">
         <f t="shared" si="3"/>
-        <v>58.581999999999994</v>
+        <v>208.58199999999999</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -7423,11 +7429,11 @@
       </c>
       <c r="C6" s="61">
         <f>IFERROR(IF(SUMIF('Rent Collections'!$B$2:$B$10007,A6,'Rent Collections'!$E$2:$E$10007)=0,"No data",SUMIF('Rent Collections'!$B$2:$B$10007,A6,'Rent Collections'!$E$2:$E$10007)/(COUNTIFS('Rent Collections'!$B$2:$B$10000,"1053 Ridgeway Avenue")-1)),"No data")</f>
-        <v>765</v>
+        <v>1105</v>
       </c>
       <c r="D6" s="36">
         <f t="shared" si="0"/>
-        <v>-135</v>
+        <v>205</v>
       </c>
       <c r="E6" s="35">
         <f>IFERROR(Inputs!H7,"N/A")</f>
@@ -7447,11 +7453,11 @@
       </c>
       <c r="I6" s="36">
         <f t="shared" si="2"/>
-        <v>727.23</v>
+        <v>1067.23</v>
       </c>
       <c r="J6" s="42">
         <f>IFERROR(IF(I6="No data","No data",I6-H6),"No data")</f>
-        <v>-52.769999999999982</v>
+        <v>287.23</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -7465,11 +7471,11 @@
       </c>
       <c r="C7" s="61">
         <f>IFERROR(IF(SUMIF('Rent Collections'!$B$2:$B$10007,A7,'Rent Collections'!$E$2:$E$10007)=0,"No data",SUMIF('Rent Collections'!$B$2:$B$10007,A7,'Rent Collections'!$E$2:$E$10007)/(COUNTIFS('Rent Collections'!$B$2:$B$10000,"1053 Ridgeway Avenue")-1)),"No data")</f>
-        <v>935</v>
+        <v>1115</v>
       </c>
       <c r="D7" s="36">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>215</v>
       </c>
       <c r="E7" s="35">
         <f>IFERROR(Inputs!H8,"N/A")</f>
@@ -7489,11 +7495,11 @@
       </c>
       <c r="I7" s="36">
         <f t="shared" si="2"/>
-        <v>852.05200000000002</v>
+        <v>1032.0519999999999</v>
       </c>
       <c r="J7" s="42">
         <f t="shared" si="3"/>
-        <v>72.052000000000021</v>
+        <v>252.05199999999991</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -7507,11 +7513,11 @@
       </c>
       <c r="C8" s="61">
         <f>IFERROR(IF(SUMIF('Rent Collections'!$B$2:$B$10007,A8,'Rent Collections'!$E$2:$E$10007)=0,"No data",SUMIF('Rent Collections'!$B$2:$B$10007,A8,'Rent Collections'!$E$2:$E$10007)/(COUNTIFS('Rent Collections'!$B$2:$B$10000,"1053 Ridgeway Avenue")-1)),"No data")</f>
-        <v>800</v>
+        <v>960</v>
       </c>
       <c r="D8" s="36">
         <f>IFERROR(IF(C8="No data","No data",C8-B8),"No data")</f>
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="E8" s="35">
         <f>IFERROR(Inputs!H9,"N/A")</f>
@@ -7531,11 +7537,11 @@
       </c>
       <c r="I8" s="36">
         <f>IFERROR(IF(OR(C8="No data",F8="No data"),"No data",C8-F8),"No data")</f>
-        <v>796.08600000000001</v>
+        <v>956.08600000000001</v>
       </c>
       <c r="J8" s="42">
         <f t="shared" si="3"/>
-        <v>102.75266666666664</v>
+        <v>262.75266666666664</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -7549,11 +7555,11 @@
       </c>
       <c r="C9" s="61">
         <f>IFERROR(IF(SUMIF('Rent Collections'!$B$2:$B$10007,A9,'Rent Collections'!$E$2:$E$10007)=0,"No data",SUMIF('Rent Collections'!$B$2:$B$10007,A9,'Rent Collections'!$E$2:$E$10007)/(COUNTIFS('Rent Collections'!$B$2:$B$10000,"1053 Ridgeway Avenue")-1)),"No data")</f>
-        <v>525</v>
+        <v>630</v>
       </c>
       <c r="D9" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="E9" s="35">
         <f>IFERROR(Inputs!H10,"N/A")</f>
@@ -7573,11 +7579,11 @@
       </c>
       <c r="I9" s="36">
         <f t="shared" si="2"/>
-        <v>525</v>
+        <v>630</v>
       </c>
       <c r="J9" s="42">
         <f t="shared" si="3"/>
-        <v>54.25</v>
+        <v>159.25</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -7591,11 +7597,11 @@
       </c>
       <c r="C10" s="61">
         <f>IFERROR(IF(SUMIF('Rent Collections'!$B$2:$B$10007,A10,'Rent Collections'!$E$2:$E$10007)=0,"No data",SUMIF('Rent Collections'!$B$2:$B$10007,A10,'Rent Collections'!$E$2:$E$10007)/(COUNTIFS('Rent Collections'!$B$2:$B$10000,"1053 Ridgeway Avenue")-1)),"No data")</f>
-        <v>850</v>
+        <v>1020</v>
       </c>
       <c r="D10" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="E10" s="35">
         <f>IFERROR(Inputs!H11,"N/A")</f>
@@ -7615,11 +7621,11 @@
       </c>
       <c r="I10" s="36">
         <f t="shared" si="2"/>
-        <v>674.14200000000005</v>
+        <v>844.14200000000005</v>
       </c>
       <c r="J10" s="42">
         <f t="shared" si="3"/>
-        <v>-62.524666666666576</v>
+        <v>107.47533333333342</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -7633,11 +7639,11 @@
       </c>
       <c r="C11" s="61">
         <f>IFERROR(IF(SUMIF('Rent Collections'!$B$2:$B$10007,A11,'Rent Collections'!$E$2:$E$10007)=0,"No data",SUMIF('Rent Collections'!$B$2:$B$10007,A11,'Rent Collections'!$E$2:$E$10007)/(COUNTIFS('Rent Collections'!$B$2:$B$10000,"1053 Ridgeway Avenue")-1)),"No data")</f>
-        <v>525</v>
+        <v>630</v>
       </c>
       <c r="D11" s="36">
         <f t="shared" si="0"/>
-        <v>-325</v>
+        <v>-220</v>
       </c>
       <c r="E11" s="35">
         <f>IFERROR(Inputs!H12,"N/A")</f>
@@ -7657,11 +7663,11 @@
       </c>
       <c r="I11" s="36">
         <f t="shared" si="2"/>
-        <v>525</v>
+        <v>630</v>
       </c>
       <c r="J11" s="42">
         <f t="shared" si="3"/>
-        <v>-211.66666666666663</v>
+        <v>-106.66666666666663</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -7675,11 +7681,11 @@
       </c>
       <c r="C12" s="61">
         <f>IFERROR(IF(SUMIF('Rent Collections'!$B$2:$B$10007,A12,'Rent Collections'!$E$2:$E$10007)=0,"No data",SUMIF('Rent Collections'!$B$2:$B$10007,A12,'Rent Collections'!$E$2:$E$10007)/(COUNTIFS('Rent Collections'!$B$2:$B$10000,"1053 Ridgeway Avenue")-1)),"No data")</f>
-        <v>850</v>
+        <v>1020</v>
       </c>
       <c r="D12" s="36">
         <f t="shared" si="0"/>
-        <v>325</v>
+        <v>495</v>
       </c>
       <c r="E12" s="35">
         <f>IFERROR(Inputs!H13,"N/A")</f>
@@ -7699,11 +7705,11 @@
       </c>
       <c r="I12" s="36">
         <f t="shared" si="2"/>
-        <v>850</v>
+        <v>1020</v>
       </c>
       <c r="J12" s="42">
         <f t="shared" si="3"/>
-        <v>395</v>
+        <v>565</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -8896,7 +8902,9 @@
         <f>IF(D2="","",D2-E2)</f>
         <v>0</v>
       </c>
-      <c r="H2" s="31"/>
+      <c r="H2" s="31" t="s">
+        <v>71</v>
+      </c>
       <c r="I2" s="32" t="str">
         <f>IF(RentCollectionsTable[[#This Row],[Amount due]]="","",IF(RentCollectionsTable[[#This Row],[Balance Remaining]]&gt;0,"Partial","Paid in full"))</f>
         <v>Paid in full</v>
@@ -8910,7 +8918,7 @@
         <v>43</v>
       </c>
       <c r="C3" s="26" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D3" s="27">
         <v>475</v>
@@ -8925,13 +8933,15 @@
         <f>IF(D3="","",D3-E3)</f>
         <v>0</v>
       </c>
-      <c r="H3" s="31"/>
+      <c r="H3" s="31" t="s">
+        <v>71</v>
+      </c>
       <c r="I3" s="27" t="str">
         <f>IF(RentCollectionsTable[[#This Row],[Amount due]]="","",IF(RentCollectionsTable[[#This Row],[Balance Remaining]]&gt;0,"Partial","Paid in full"))</f>
         <v>Paid in full</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="60.75">
+    <row r="4" spans="1:9" ht="76.5">
       <c r="A4" s="29">
         <v>46023</v>
       </c>
@@ -8939,7 +8949,7 @@
         <v>46</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D4" s="27">
         <v>900</v>
@@ -8955,7 +8965,7 @@
         <v>-150</v>
       </c>
       <c r="H4" s="63" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I4" s="27" t="str">
         <f>IF(RentCollectionsTable[[#This Row],[Amount due]]="","",IF(RentCollectionsTable[[#This Row],[Balance Remaining]]&gt;0,"Partial","Paid in full"))</f>
@@ -8970,7 +8980,7 @@
         <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D5" s="27">
         <v>900</v>
@@ -8985,13 +8995,15 @@
         <f>IF(D5="","",D5-E5)</f>
         <v>0</v>
       </c>
-      <c r="H5" s="31"/>
+      <c r="H5" s="31" t="s">
+        <v>71</v>
+      </c>
       <c r="I5" s="27" t="str">
         <f>IF(RentCollectionsTable[[#This Row],[Amount due]]="","",IF(RentCollectionsTable[[#This Row],[Balance Remaining]]&gt;0,"Partial","Paid in full"))</f>
         <v>Paid in full</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="30.75">
+    <row r="6" spans="1:9" ht="45.75">
       <c r="A6" s="29">
         <v>46024</v>
       </c>
@@ -8999,7 +9011,7 @@
         <v>47</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D6" s="23">
         <v>800</v>
@@ -9015,7 +9027,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="52" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I6" s="23" t="str">
         <f>IF(RentCollectionsTable[[#This Row],[Amount due]]="","",IF(RentCollectionsTable[[#This Row],[Balance Remaining]]&gt;0,"Partial","Paid in full"))</f>
@@ -9030,7 +9042,7 @@
         <v>48</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D7" s="23">
         <v>525</v>
@@ -9045,7 +9057,9 @@
         <f>IF(D7="","",D7-E7)</f>
         <v>0</v>
       </c>
-      <c r="H7" s="49"/>
+      <c r="H7" s="49" t="s">
+        <v>71</v>
+      </c>
       <c r="I7" s="23" t="str">
         <f>IF(RentCollectionsTable[[#This Row],[Amount due]]="","",IF(RentCollectionsTable[[#This Row],[Balance Remaining]]&gt;0,"Partial","Paid in full"))</f>
         <v>Paid in full</v>
@@ -9059,7 +9073,7 @@
         <v>49</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D8" s="23">
         <v>850</v>
@@ -9074,7 +9088,9 @@
         <f>IF(D8="","",D8-E8)</f>
         <v>0</v>
       </c>
-      <c r="H8" s="49"/>
+      <c r="H8" s="49" t="s">
+        <v>71</v>
+      </c>
       <c r="I8" s="23" t="str">
         <f>IF(RentCollectionsTable[[#This Row],[Amount due]]="","",IF(RentCollectionsTable[[#This Row],[Balance Remaining]]&gt;0,"Partial","Paid in full"))</f>
         <v>Paid in full</v>
@@ -9088,7 +9104,7 @@
         <v>50</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D9" s="23">
         <v>525</v>
@@ -9103,7 +9119,9 @@
         <f>IF(D9="","",D9-E9)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="49"/>
+      <c r="H9" s="49" t="s">
+        <v>71</v>
+      </c>
       <c r="I9" s="23" t="str">
         <f>IF(RentCollectionsTable[[#This Row],[Amount due]]="","",IF(RentCollectionsTable[[#This Row],[Balance Remaining]]&gt;0,"Partial","Paid in full"))</f>
         <v>Paid in full</v>
@@ -9117,7 +9135,7 @@
         <v>44</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D10" s="23">
         <v>750</v>
@@ -9132,7 +9150,9 @@
         <f>IF(D10="","",D10-E10)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="49"/>
+      <c r="H10" s="49" t="s">
+        <v>71</v>
+      </c>
       <c r="I10" s="23" t="str">
         <f>IF(RentCollectionsTable[[#This Row],[Amount due]]="","",IF(RentCollectionsTable[[#This Row],[Balance Remaining]]&gt;0,"Partial","Paid in full"))</f>
         <v>Paid in full</v>
@@ -9146,7 +9166,7 @@
         <v>51</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D11" s="23">
         <v>850</v>
@@ -9161,7 +9181,9 @@
         <f>IF(D11="","",D11-E11)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="49"/>
+      <c r="H11" s="49" t="s">
+        <v>71</v>
+      </c>
       <c r="I11" s="23" t="str">
         <f>IF(RentCollectionsTable[[#This Row],[Amount due]]="","",IF(RentCollectionsTable[[#This Row],[Balance Remaining]]&gt;0,"Partial","Paid in full"))</f>
         <v>Paid in full</v>
@@ -9175,7 +9197,7 @@
         <v>45</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D12" s="23">
         <v>900</v>
@@ -9191,7 +9213,7 @@
         <v>-25</v>
       </c>
       <c r="H12" s="49" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I12" s="23" t="str">
         <f>IF(RentCollectionsTable[[#This Row],[Amount due]]="","",IF(RentCollectionsTable[[#This Row],[Balance Remaining]]&gt;0,"Partial","Paid in full"))</f>
@@ -9235,7 +9257,7 @@
         <v>43</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D14" s="23">
         <v>475</v>
@@ -9264,7 +9286,7 @@
         <v>45</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D15" s="23">
         <v>900</v>
@@ -9280,7 +9302,7 @@
         <v>-100</v>
       </c>
       <c r="H15" s="52" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I15" s="23" t="str">
         <f>IF(RentCollectionsTable[[#This Row],[Amount due]]="","",IF(RentCollectionsTable[[#This Row],[Balance Remaining]]&gt;0,"Partial","Paid in full"))</f>
@@ -9295,7 +9317,7 @@
         <v>46</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" s="23">
         <v>900</v>
@@ -9324,7 +9346,7 @@
         <v>48</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D17" s="23">
         <v>525</v>
@@ -9353,7 +9375,7 @@
         <v>49</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D18" s="23">
         <v>850</v>
@@ -9369,7 +9391,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="52" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I18" s="23" t="str">
         <f>IF(RentCollectionsTable[[#This Row],[Amount due]]="","",IF(RentCollectionsTable[[#This Row],[Balance Remaining]]&gt;0,"Partial","Paid in full"))</f>
@@ -9384,7 +9406,7 @@
         <v>50</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D19" s="23">
         <v>525</v>
@@ -9413,7 +9435,7 @@
         <v>51</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D20" s="23">
         <v>850</v>
@@ -9442,7 +9464,7 @@
         <v>42</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D21" s="23">
         <v>900</v>
@@ -9471,7 +9493,7 @@
         <v>44</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D22" s="23">
         <v>750</v>
@@ -9500,7 +9522,7 @@
         <v>47</v>
       </c>
       <c r="C23" s="26" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D23" s="27">
         <v>800</v>
@@ -9558,7 +9580,7 @@
         <v>43</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D25" s="23">
         <v>475</v>
@@ -9587,7 +9609,7 @@
         <v>49</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D26" s="23">
         <v>850</v>
@@ -9616,7 +9638,7 @@
         <v>50</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D27" s="23">
         <v>525</v>
@@ -9645,7 +9667,7 @@
         <v>48</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D28" s="23">
         <v>525</v>
@@ -9674,7 +9696,7 @@
         <v>51</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D29" s="23">
         <v>850</v>
@@ -9703,7 +9725,7 @@
         <v>44</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D30" s="23">
         <v>750</v>
@@ -9732,7 +9754,7 @@
         <v>42</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D31" s="23">
         <v>900</v>
@@ -9753,7 +9775,7 @@
         <v>Paid in full</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="45.75">
+    <row r="32" spans="1:9">
       <c r="A32" s="50">
         <v>46087</v>
       </c>
@@ -9761,27 +9783,25 @@
         <v>45</v>
       </c>
       <c r="C32" s="22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D32" s="23">
         <v>900</v>
       </c>
       <c r="E32" s="23">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="F32" s="22" t="s">
         <v>70</v>
       </c>
       <c r="G32" s="23">
         <f>IF(D32="","",D32-E32)</f>
-        <v>800</v>
-      </c>
-      <c r="H32" s="52" t="s">
-        <v>86</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H32" s="52"/>
       <c r="I32" s="23" t="str">
         <f>IF(RentCollectionsTable[[#This Row],[Amount due]]="","",IF(RentCollectionsTable[[#This Row],[Balance Remaining]]&gt;0,"Partial","Paid in full"))</f>
-        <v>Partial</v>
+        <v>Paid in full</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -9792,7 +9812,7 @@
         <v>47</v>
       </c>
       <c r="C33" s="22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D33" s="23">
         <v>800</v>
@@ -9821,7 +9841,7 @@
         <v>46</v>
       </c>
       <c r="C34" s="26" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D34" s="27">
         <v>900</v>
@@ -9837,7 +9857,7 @@
         <v>-25</v>
       </c>
       <c r="H34" s="31" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I34" s="27" t="str">
         <f>IF(RentCollectionsTable[[#This Row],[Amount due]]="","",IF(RentCollectionsTable[[#This Row],[Balance Remaining]]&gt;0,"Partial","Paid in full"))</f>
@@ -9883,7 +9903,7 @@
         <v>43</v>
       </c>
       <c r="C36" s="22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D36" s="23">
         <v>475</v>
@@ -9898,7 +9918,9 @@
         <f>IF(D36="","",D36-E36)</f>
         <v>0</v>
       </c>
-      <c r="H36" s="49"/>
+      <c r="H36" s="49" t="s">
+        <v>71</v>
+      </c>
       <c r="I36" s="23" t="str">
         <f>IF(RentCollectionsTable[[#This Row],[Amount due]]="","",IF(RentCollectionsTable[[#This Row],[Balance Remaining]]&gt;0,"Partial","Paid in full"))</f>
         <v>Paid in full</v>
@@ -9912,7 +9934,7 @@
         <v>44</v>
       </c>
       <c r="C37" s="22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D37" s="23">
         <v>750</v>
@@ -9927,7 +9949,9 @@
         <f>IF(D37="","",D37-E37)</f>
         <v>0</v>
       </c>
-      <c r="H37" s="49"/>
+      <c r="H37" s="49" t="s">
+        <v>71</v>
+      </c>
       <c r="I37" s="23" t="str">
         <f>IF(RentCollectionsTable[[#This Row],[Amount due]]="","",IF(RentCollectionsTable[[#This Row],[Balance Remaining]]&gt;0,"Partial","Paid in full"))</f>
         <v>Paid in full</v>
@@ -9941,7 +9965,7 @@
         <v>46</v>
       </c>
       <c r="C38" s="22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D38" s="23">
         <v>900</v>
@@ -9956,7 +9980,9 @@
         <f>IF(D38="","",D38-E38)</f>
         <v>0</v>
       </c>
-      <c r="H38" s="49"/>
+      <c r="H38" s="49" t="s">
+        <v>71</v>
+      </c>
       <c r="I38" s="23" t="str">
         <f>IF(RentCollectionsTable[[#This Row],[Amount due]]="","",IF(RentCollectionsTable[[#This Row],[Balance Remaining]]&gt;0,"Partial","Paid in full"))</f>
         <v>Paid in full</v>
@@ -9970,7 +9996,7 @@
         <v>49</v>
       </c>
       <c r="C39" s="22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D39" s="23">
         <v>850</v>
@@ -9985,7 +10011,9 @@
         <f>IF(D39="","",D39-E39)</f>
         <v>0</v>
       </c>
-      <c r="H39" s="49"/>
+      <c r="H39" s="49" t="s">
+        <v>71</v>
+      </c>
       <c r="I39" s="23" t="str">
         <f>IF(RentCollectionsTable[[#This Row],[Amount due]]="","",IF(RentCollectionsTable[[#This Row],[Balance Remaining]]&gt;0,"Partial","Paid in full"))</f>
         <v>Paid in full</v>
@@ -9999,7 +10027,7 @@
         <v>51</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D40" s="23">
         <v>850</v>
@@ -10014,7 +10042,9 @@
         <f>IF(D40="","",D40-E40)</f>
         <v>0</v>
       </c>
-      <c r="H40" s="49"/>
+      <c r="H40" s="49" t="s">
+        <v>71</v>
+      </c>
       <c r="I40" s="23" t="str">
         <f>IF(RentCollectionsTable[[#This Row],[Amount due]]="","",IF(RentCollectionsTable[[#This Row],[Balance Remaining]]&gt;0,"Partial","Paid in full"))</f>
         <v>Paid in full</v>
@@ -10028,7 +10058,7 @@
         <v>42</v>
       </c>
       <c r="C41" s="22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D41" s="23">
         <v>900</v>
@@ -10043,7 +10073,9 @@
         <f>IF(D41="","",D41-E41)</f>
         <v>0</v>
       </c>
-      <c r="H41" s="49"/>
+      <c r="H41" s="49" t="s">
+        <v>71</v>
+      </c>
       <c r="I41" s="23" t="str">
         <f>IF(RentCollectionsTable[[#This Row],[Amount due]]="","",IF(RentCollectionsTable[[#This Row],[Balance Remaining]]&gt;0,"Partial","Paid in full"))</f>
         <v>Paid in full</v>
@@ -10057,7 +10089,7 @@
         <v>47</v>
       </c>
       <c r="C42" s="22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D42" s="23">
         <v>800</v>
@@ -10072,7 +10104,9 @@
         <f>IF(D42="","",D42-E42)</f>
         <v>0</v>
       </c>
-      <c r="H42" s="49"/>
+      <c r="H42" s="49" t="s">
+        <v>71</v>
+      </c>
       <c r="I42" s="23" t="str">
         <f>IF(RentCollectionsTable[[#This Row],[Amount due]]="","",IF(RentCollectionsTable[[#This Row],[Balance Remaining]]&gt;0,"Partial","Paid in full"))</f>
         <v>Paid in full</v>
@@ -10086,7 +10120,7 @@
         <v>48</v>
       </c>
       <c r="C43" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D43" s="23">
         <v>525</v>
@@ -10101,7 +10135,9 @@
         <f>IF(D43="","",D43-E43)</f>
         <v>0</v>
       </c>
-      <c r="H43" s="49"/>
+      <c r="H43" s="49" t="s">
+        <v>71</v>
+      </c>
       <c r="I43" s="23" t="str">
         <f>IF(RentCollectionsTable[[#This Row],[Amount due]]="","",IF(RentCollectionsTable[[#This Row],[Balance Remaining]]&gt;0,"Partial","Paid in full"))</f>
         <v>Paid in full</v>
@@ -10115,7 +10151,7 @@
         <v>50</v>
       </c>
       <c r="C44" s="22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D44" s="23">
         <v>525</v>
@@ -10130,7 +10166,9 @@
         <f>IF(D44="","",D44-E44)</f>
         <v>0</v>
       </c>
-      <c r="H44" s="49"/>
+      <c r="H44" s="49" t="s">
+        <v>71</v>
+      </c>
       <c r="I44" s="23" t="str">
         <f>IF(RentCollectionsTable[[#This Row],[Amount due]]="","",IF(RentCollectionsTable[[#This Row],[Balance Remaining]]&gt;0,"Partial","Paid in full"))</f>
         <v>Paid in full</v>
@@ -10144,7 +10182,7 @@
         <v>45</v>
       </c>
       <c r="C45" s="26" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D45" s="27">
         <v>900</v>
@@ -10159,7 +10197,9 @@
         <f>IF(D45="","",D45-E45)</f>
         <v>0</v>
       </c>
-      <c r="H45" s="31"/>
+      <c r="H45" s="49" t="s">
+        <v>71</v>
+      </c>
       <c r="I45" s="27" t="str">
         <f>IF(RentCollectionsTable[[#This Row],[Amount due]]="","",IF(RentCollectionsTable[[#This Row],[Balance Remaining]]&gt;0,"Partial","Paid in full"))</f>
         <v>Paid in full</v>
@@ -10202,7 +10242,7 @@
         <v>43</v>
       </c>
       <c r="C47" s="22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D47" s="23">
         <v>475</v>
@@ -10231,7 +10271,7 @@
         <v>46</v>
       </c>
       <c r="C48" s="22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D48" s="23">
         <v>900</v>
@@ -10260,7 +10300,7 @@
         <v>47</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D49" s="23">
         <v>800</v>
@@ -10289,7 +10329,7 @@
         <v>49</v>
       </c>
       <c r="C50" s="22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D50" s="23">
         <v>850</v>
@@ -10318,7 +10358,7 @@
         <v>51</v>
       </c>
       <c r="C51" s="22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D51" s="23">
         <v>850</v>
@@ -10347,7 +10387,7 @@
         <v>45</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D52" s="23">
         <v>900</v>
@@ -10376,7 +10416,7 @@
         <v>42</v>
       </c>
       <c r="C53" s="22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D53" s="23">
         <v>900</v>
@@ -10407,7 +10447,7 @@
         <v>44</v>
       </c>
       <c r="C54" s="22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D54" s="23">
         <v>750</v>
@@ -10436,7 +10476,7 @@
         <v>48</v>
       </c>
       <c r="C55" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D55" s="23">
         <v>525</v>
@@ -10457,7 +10497,7 @@
         <v>Paid in full</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" ht="76.5">
       <c r="A56" s="50">
         <v>46147</v>
       </c>
@@ -10465,7 +10505,7 @@
         <v>50</v>
       </c>
       <c r="C56" s="26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D56" s="27">
         <v>525</v>
@@ -10480,7 +10520,9 @@
         <f>IF(D56="","",D56-E56)</f>
         <v>0</v>
       </c>
-      <c r="H56" s="31"/>
+      <c r="H56" s="63" t="s">
+        <v>89</v>
+      </c>
       <c r="I56" s="27" t="str">
         <f>IF(RentCollectionsTable[[#This Row],[Amount due]]="","",IF(RentCollectionsTable[[#This Row],[Balance Remaining]]&gt;0,"Partial","Paid in full"))</f>
         <v>Paid in full</v>
@@ -10499,18 +10541,20 @@
       <c r="D57" s="23">
         <v>800</v>
       </c>
-      <c r="E57" s="23"/>
+      <c r="E57" s="23">
+        <v>800</v>
+      </c>
       <c r="F57" s="22" t="s">
         <v>70</v>
       </c>
       <c r="G57" s="23">
         <f>IF(D57="","",D57-E57)</f>
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="H57" s="49"/>
       <c r="I57" s="23" t="str">
         <f>IF(RentCollectionsTable[[#This Row],[Amount due]]="","",IF(RentCollectionsTable[[#This Row],[Balance Remaining]]&gt;0,"Partial","Paid in full"))</f>
-        <v>Partial</v>
+        <v>Paid in full</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -10521,23 +10565,25 @@
         <v>42</v>
       </c>
       <c r="C58" s="22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D58" s="23">
         <v>900</v>
       </c>
-      <c r="E58" s="23"/>
+      <c r="E58" s="23">
+        <v>900</v>
+      </c>
       <c r="F58" s="22" t="s">
         <v>70</v>
       </c>
       <c r="G58" s="23">
         <f>IF(D58="","",D58-E58)</f>
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="H58" s="49"/>
       <c r="I58" s="23" t="str">
         <f>IF(RentCollectionsTable[[#This Row],[Amount due]]="","",IF(RentCollectionsTable[[#This Row],[Balance Remaining]]&gt;0,"Partial","Paid in full"))</f>
-        <v>Partial</v>
+        <v>Paid in full</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="30.75">
@@ -10548,23 +10594,25 @@
         <v>43</v>
       </c>
       <c r="C59" s="22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D59" s="23">
         <v>475</v>
       </c>
-      <c r="E59" s="23"/>
+      <c r="E59" s="23">
+        <v>475</v>
+      </c>
       <c r="F59" s="22" t="s">
         <v>70</v>
       </c>
       <c r="G59" s="23">
         <f>IF(D59="","",D59-E59)</f>
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="H59" s="49"/>
       <c r="I59" s="23" t="str">
         <f>IF(RentCollectionsTable[[#This Row],[Amount due]]="","",IF(RentCollectionsTable[[#This Row],[Balance Remaining]]&gt;0,"Partial","Paid in full"))</f>
-        <v>Partial</v>
+        <v>Paid in full</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -10575,23 +10623,25 @@
         <v>44</v>
       </c>
       <c r="C60" s="22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D60" s="23">
         <v>750</v>
       </c>
-      <c r="E60" s="23"/>
+      <c r="E60" s="23">
+        <v>750</v>
+      </c>
       <c r="F60" s="22" t="s">
         <v>70</v>
       </c>
       <c r="G60" s="23">
         <f>IF(D60="","",D60-E60)</f>
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="H60" s="49"/>
       <c r="I60" s="23" t="str">
         <f>IF(RentCollectionsTable[[#This Row],[Amount due]]="","",IF(RentCollectionsTable[[#This Row],[Balance Remaining]]&gt;0,"Partial","Paid in full"))</f>
-        <v>Partial</v>
+        <v>Paid in full</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -10602,23 +10652,25 @@
         <v>45</v>
       </c>
       <c r="C61" s="22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D61" s="23">
         <v>900</v>
       </c>
-      <c r="E61" s="23"/>
+      <c r="E61" s="23">
+        <v>900</v>
+      </c>
       <c r="F61" s="22" t="s">
         <v>70</v>
       </c>
       <c r="G61" s="23">
         <f>IF(D61="","",D61-E61)</f>
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="H61" s="49"/>
       <c r="I61" s="23" t="str">
         <f>IF(RentCollectionsTable[[#This Row],[Amount due]]="","",IF(RentCollectionsTable[[#This Row],[Balance Remaining]]&gt;0,"Partial","Paid in full"))</f>
-        <v>Partial</v>
+        <v>Paid in full</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -10629,26 +10681,28 @@
         <v>46</v>
       </c>
       <c r="C62" s="22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D62" s="23">
         <v>900</v>
       </c>
-      <c r="E62" s="23"/>
+      <c r="E62" s="23">
+        <v>900</v>
+      </c>
       <c r="F62" s="22" t="s">
         <v>70</v>
       </c>
       <c r="G62" s="23">
         <f>IF(D62="","",D62-E62)</f>
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="H62" s="49"/>
       <c r="I62" s="23" t="str">
         <f>IF(RentCollectionsTable[[#This Row],[Amount due]]="","",IF(RentCollectionsTable[[#This Row],[Balance Remaining]]&gt;0,"Partial","Paid in full"))</f>
-        <v>Partial</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9">
+        <v>Paid in full</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="45.75">
       <c r="A63" s="50">
         <v>46174</v>
       </c>
@@ -10656,23 +10710,27 @@
         <v>47</v>
       </c>
       <c r="C63" s="22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D63" s="23">
         <v>800</v>
       </c>
-      <c r="E63" s="23"/>
+      <c r="E63" s="23">
+        <v>800</v>
+      </c>
       <c r="F63" s="22" t="s">
         <v>70</v>
       </c>
       <c r="G63" s="23">
         <f>IF(D63="","",D63-E63)</f>
-        <v>800</v>
-      </c>
-      <c r="H63" s="49"/>
+        <v>0</v>
+      </c>
+      <c r="H63" s="52" t="s">
+        <v>90</v>
+      </c>
       <c r="I63" s="23" t="str">
         <f>IF(RentCollectionsTable[[#This Row],[Amount due]]="","",IF(RentCollectionsTable[[#This Row],[Balance Remaining]]&gt;0,"Partial","Paid in full"))</f>
-        <v>Partial</v>
+        <v>Paid in full</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -10683,23 +10741,25 @@
         <v>48</v>
       </c>
       <c r="C64" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D64" s="23">
         <v>525</v>
       </c>
-      <c r="E64" s="23"/>
+      <c r="E64" s="23">
+        <v>525</v>
+      </c>
       <c r="F64" s="22" t="s">
         <v>70</v>
       </c>
       <c r="G64" s="23">
         <f>IF(D64="","",D64-E64)</f>
-        <v>525</v>
+        <v>0</v>
       </c>
       <c r="H64" s="49"/>
       <c r="I64" s="23" t="str">
         <f>IF(RentCollectionsTable[[#This Row],[Amount due]]="","",IF(RentCollectionsTable[[#This Row],[Balance Remaining]]&gt;0,"Partial","Paid in full"))</f>
-        <v>Partial</v>
+        <v>Paid in full</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -10710,23 +10770,25 @@
         <v>49</v>
       </c>
       <c r="C65" s="22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D65" s="23">
         <v>850</v>
       </c>
-      <c r="E65" s="23"/>
+      <c r="E65" s="23">
+        <v>850</v>
+      </c>
       <c r="F65" s="22" t="s">
         <v>70</v>
       </c>
       <c r="G65" s="23">
         <f>IF(D65="","",D65-E65)</f>
-        <v>850</v>
+        <v>0</v>
       </c>
       <c r="H65" s="49"/>
       <c r="I65" s="23" t="str">
         <f>IF(RentCollectionsTable[[#This Row],[Amount due]]="","",IF(RentCollectionsTable[[#This Row],[Balance Remaining]]&gt;0,"Partial","Paid in full"))</f>
-        <v>Partial</v>
+        <v>Paid in full</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -10737,23 +10799,25 @@
         <v>51</v>
       </c>
       <c r="C66" s="22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D66" s="23">
         <v>850</v>
       </c>
-      <c r="E66" s="23"/>
+      <c r="E66" s="23">
+        <v>850</v>
+      </c>
       <c r="F66" s="22" t="s">
         <v>70</v>
       </c>
       <c r="G66" s="23">
         <f>IF(D66="","",D66-E66)</f>
-        <v>850</v>
+        <v>0</v>
       </c>
       <c r="H66" s="49"/>
       <c r="I66" s="23" t="str">
         <f>IF(RentCollectionsTable[[#This Row],[Amount due]]="","",IF(RentCollectionsTable[[#This Row],[Balance Remaining]]&gt;0,"Partial","Paid in full"))</f>
-        <v>Partial</v>
+        <v>Paid in full</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -10764,23 +10828,25 @@
         <v>50</v>
       </c>
       <c r="C67" s="26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D67" s="27">
         <v>525</v>
       </c>
-      <c r="E67" s="23"/>
+      <c r="E67" s="23">
+        <v>525</v>
+      </c>
       <c r="F67" s="26" t="s">
         <v>70</v>
       </c>
       <c r="G67" s="27">
         <f>IF(D67="","",D67-E67)</f>
-        <v>525</v>
+        <v>0</v>
       </c>
       <c r="H67" s="31"/>
       <c r="I67" s="27" t="str">
         <f>IF(RentCollectionsTable[[#This Row],[Amount due]]="","",IF(RentCollectionsTable[[#This Row],[Balance Remaining]]&gt;0,"Partial","Paid in full"))</f>
-        <v>Partial</v>
+        <v>Paid in full</v>
       </c>
     </row>
   </sheetData>
@@ -10832,25 +10898,25 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G1" t="s">
         <v>67</v>
       </c>
       <c r="H1" s="19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I1" s="19" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -10861,16 +10927,16 @@
         <v>49</v>
       </c>
       <c r="C2" s="22" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D2" s="22" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E2" s="23">
         <v>38.950000000000003</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G2" s="22"/>
       <c r="H2" s="21" t="str">
@@ -10890,16 +10956,16 @@
         <v>54</v>
       </c>
       <c r="C3" s="26" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E3" s="27">
         <v>-165.83</v>
       </c>
       <c r="F3" s="26" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G3" s="26"/>
       <c r="H3" s="25" t="str">
@@ -10920,16 +10986,16 @@
         <v>41</v>
       </c>
       <c r="C4" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="D4" s="22" t="s">
         <v>101</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>99</v>
       </c>
       <c r="E4" s="27">
         <v>7.64</v>
       </c>
       <c r="F4" s="26" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G4" s="26"/>
       <c r="H4" s="25" t="str">
@@ -10949,16 +11015,16 @@
         <v>41</v>
       </c>
       <c r="C5" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" s="22" t="s">
         <v>101</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>99</v>
       </c>
       <c r="E5" s="23">
         <v>6.55</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G5" s="26"/>
       <c r="H5" s="25" t="str">
@@ -10978,16 +11044,16 @@
         <v>47</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D6" s="51" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E6" s="27">
         <v>19.57</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G6" s="26"/>
       <c r="H6" s="25" t="str">
@@ -11007,16 +11073,16 @@
         <v>54</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E7" s="27">
         <v>-24.99</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G7" s="26"/>
       <c r="H7" s="25" t="str">
@@ -11036,19 +11102,19 @@
         <v>49</v>
       </c>
       <c r="C8" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="D8" s="22" t="s">
         <v>101</v>
-      </c>
-      <c r="D8" s="22" t="s">
-        <v>99</v>
       </c>
       <c r="E8" s="27">
         <v>54.71</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H8" s="25" t="str">
         <f>TEXT(A8,"MM-MMM")</f>
@@ -11067,19 +11133,19 @@
         <v>41</v>
       </c>
       <c r="C9" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" s="22" t="s">
         <v>101</v>
-      </c>
-      <c r="D9" s="22" t="s">
-        <v>99</v>
       </c>
       <c r="E9" s="27">
         <v>361.79</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G9" s="34" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H9" s="25" t="str">
         <f>TEXT(A9,"MM-MMM")</f>
@@ -11098,19 +11164,19 @@
         <v>49</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E10" s="27">
         <v>785.63</v>
       </c>
       <c r="F10" s="34" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G10" s="34" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H10" s="25" t="str">
         <f>TEXT(A10,"MM-MMM")</f>
@@ -11129,19 +11195,19 @@
         <v>44</v>
       </c>
       <c r="C11" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="D11" s="22" t="s">
         <v>101</v>
-      </c>
-      <c r="D11" s="22" t="s">
-        <v>99</v>
       </c>
       <c r="E11" s="27">
         <v>47.57</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G11" s="26" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H11" s="25" t="str">
         <f>TEXT(A11,"MM-MMM")</f>
@@ -11160,19 +11226,19 @@
         <v>44</v>
       </c>
       <c r="C12" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" s="22" t="s">
         <v>101</v>
-      </c>
-      <c r="D12" s="22" t="s">
-        <v>99</v>
       </c>
       <c r="E12" s="27">
         <v>47.02</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G12" s="26" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H12" s="25" t="str">
         <f>TEXT(A12,"MM-MMM")</f>
@@ -11191,16 +11257,16 @@
         <v>54</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E13" s="23">
         <v>-494.7</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G13" s="26"/>
       <c r="H13" s="25" t="str">
@@ -11220,19 +11286,19 @@
         <v>46</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E14" s="27">
         <v>286.57</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G14" s="34" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H14" s="25" t="str">
         <f>TEXT(A14,"MM-MMM")</f>
@@ -11251,16 +11317,16 @@
         <v>46</v>
       </c>
       <c r="C15" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="D15" s="22" t="s">
         <v>101</v>
-      </c>
-      <c r="D15" s="22" t="s">
-        <v>99</v>
       </c>
       <c r="E15" s="27">
         <v>59.62</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G15" s="26"/>
       <c r="H15" s="25" t="str">
@@ -11280,16 +11346,16 @@
         <v>46</v>
       </c>
       <c r="C16" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="D16" s="22" t="s">
         <v>101</v>
-      </c>
-      <c r="D16" s="22" t="s">
-        <v>99</v>
       </c>
       <c r="E16" s="27">
         <v>18.29</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G16" s="26"/>
       <c r="H16" s="25" t="str">
@@ -11309,16 +11375,16 @@
         <v>46</v>
       </c>
       <c r="C17" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" s="26" t="s">
         <v>101</v>
-      </c>
-      <c r="D17" s="26" t="s">
-        <v>99</v>
       </c>
       <c r="E17" s="27">
         <v>50.26</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G17" s="26"/>
       <c r="H17" s="25" t="str">
@@ -11338,16 +11404,16 @@
         <v>45</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D18" s="34" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E18" s="27">
         <v>3000</v>
       </c>
       <c r="F18" s="34" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G18" s="26"/>
       <c r="H18" s="25" t="str">
@@ -11367,19 +11433,19 @@
         <v>45</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E19" s="27">
         <v>-2811.15</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G19" s="26" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H19" s="25" t="str">
         <f>TEXT(A19,"MM-MMM")</f>
@@ -11436,20 +11502,20 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.75">
       <c r="A1" s="9" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="48" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="22" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B4" s="66">
         <v>785.63</v>
@@ -11457,7 +11523,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="22" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B5" s="66">
         <v>38.950000000000003</v>
@@ -11465,7 +11531,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="22" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B6" s="66">
         <v>-685.52</v>
@@ -11473,7 +11539,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="22" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B7" s="66">
         <v>1148.44</v>
@@ -11481,7 +11547,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="22" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B8" s="66">
         <v>1287.5</v>
@@ -11489,7 +11555,7 @@
     </row>
     <row r="10" spans="1:8" ht="18.75">
       <c r="A10" s="9" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -11504,10 +11570,10 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="47" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C12" s="47" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -11515,25 +11581,25 @@
         <v>2</v>
       </c>
       <c r="B13" s="48" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C13" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="G13" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="H13" s="22" t="s">
         <v>130</v>
-      </c>
-      <c r="D13" s="22" t="s">
-        <v>131</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="F13" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="G13" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="H13" s="22" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -11651,7 +11717,7 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="22" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B21" s="22"/>
       <c r="C21" s="66">
